--- a/input/Set_and_Control_Parameters.xlsx
+++ b/input/Set_and_Control_Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo-ENS\endemo\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo_Projects\endemo-ENS\endemo_IND_world_branch\endemo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C02748-54C6-42BA-B311-F417915FDA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D5FFDC-7AD7-4001-B453-C55B6F0DFA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1020" windowWidth="20175" windowHeight="13230" tabRatio="730" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralSettings" sheetId="1" r:id="rId1"/>
@@ -59,116 +59,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="132">
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Bulgaria</t>
-  </si>
-  <si>
-    <t>Czechia</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Greece</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Croatia</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>Latvia</t>
-  </si>
-  <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Slovakia</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
-    <t>Montenegro</t>
-  </si>
-  <si>
-    <t>North Macedonia</t>
-  </si>
-  <si>
-    <t>Albania</t>
-  </si>
-  <si>
-    <t>Serbia</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina</t>
-  </si>
-  <si>
     <t>Forecast year</t>
   </si>
   <si>
-    <t>Lithuania</t>
-  </si>
-  <si>
-    <t>Estonia</t>
-  </si>
-  <si>
-    <t>Iceland</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -415,9 +313,6 @@
     <t>unspecified industry</t>
   </si>
   <si>
-    <t>allways active</t>
-  </si>
-  <si>
     <t>Scenario selection for final energy demand calaculation - electricity and hydrogen vehicles shares</t>
   </si>
   <si>
@@ -542,6 +437,24 @@
   </si>
   <si>
     <t>exp</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>olefins</t>
+  </si>
+  <si>
+    <t>olefins_classic</t>
+  </si>
+  <si>
+    <t>Ln GDP function</t>
+  </si>
+  <si>
+    <t>Last year of the historical data to be considered</t>
+  </si>
+  <si>
+    <t>Last considered year</t>
   </si>
 </sst>
 </file>
@@ -711,59 +624,59 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$4" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$3" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="C4" lockText="1" noThreeD="1"/>
+<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$2" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
+<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$6" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$7" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$8" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$9" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$10" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$11" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$4" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$4" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$12" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$10" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$13" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$12" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$14" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$13" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$15" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$14" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
@@ -771,215 +684,95 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$17" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$23" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$18" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$24" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$19" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$25" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$20" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$11" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$17" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$20" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$22" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$19" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$18" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$3" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$4" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$15" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$21" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$22" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$23" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$24" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$25" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$26" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$27" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$28" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$29" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$30" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$26" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$31" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$6" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$6" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$32" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$2" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$34" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$35" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$33" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$4" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$3" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$2" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$6" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$3" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$7" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$7" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$8" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$9" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$10" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$12" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$13" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$14" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$15" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$21" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$22" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$7" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$8" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$23" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$11" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$16" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$19" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$20" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$18" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$17" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$3" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$4" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$5" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$9" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$2" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$3" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$9" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$11" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$11" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1853,2844 +1646,6 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1033" name="Check Box 9" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1033"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1034" name="Check Box 10" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1034"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1035" name="Check Box 11" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1035"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1036" name="Check Box 12" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1036"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1037" name="Check Box 13" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1037"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1038" name="Check Box 14" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1038"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1039" name="Check Box 15" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1039"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1092" name="Check Box 68" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000044040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1093" name="Check Box 69" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000045040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1094" name="Check Box 70" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000046040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1095" name="Check Box 71" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000047040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1096" name="Check Box 72" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000048040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1097" name="Check Box 73" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000049040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1098" name="Check Box 74" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004A040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1099" name="Check Box 75" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004B040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1100" name="Check Box 76" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004C040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1101" name="Check Box 77" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004D040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1102" name="Check Box 78" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004E040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1103" name="Check Box 79" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004F040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1104" name="Check Box 80" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000050040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1105" name="Check Box 81" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000051040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1106" name="Check Box 82" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000052040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1107" name="Check Box 83" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000053040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1108" name="Check Box 84" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000054040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1109" name="Check Box 85" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000055040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1110" name="Check Box 86" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000056040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1111" name="Check Box 87" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000057040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1112" name="Check Box 88" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000058040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1113" name="Check Box 89" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000059040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1114" name="Check Box 90" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005A040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>171450</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1115" name="Check Box 91" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005B040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1116" name="Check Box 92" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005C040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>752475</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1117" name="Check Box 93" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00005D040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>Activate</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -5825,14 +2780,14 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5911,13 +2866,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -5997,13 +2952,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6083,13 +3038,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6255,13 +3210,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6341,13 +3296,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6427,13 +3382,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6513,13 +3468,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6599,13 +3554,13 @@
         <xdr:from>
           <xdr:col>1</xdr:col>
           <xdr:colOff>19050</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
           <xdr:colOff>742950</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -6789,6 +3744,264 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-0000292C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Activate</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>733425</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11307" name="Check Box 43" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s11307"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002B2C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Activate</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>19050</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>171450</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>742950</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11308" name="Check Box 44" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s11308"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002C2C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Activate</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>19050</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>742950</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11309" name="Check Box 45" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s11309"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002D2C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7415,33 +4628,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5">
         <v>2050</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5">
         <v>2050</v>
@@ -7449,114 +4662,114 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C4" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C10" s="5">
         <v>2016</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="E10" s="5">
         <v>2016</v>
@@ -7564,31 +4777,31 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -7810,7 +5023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -7822,285 +5035,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="C2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8128,732 +5077,6 @@
                     <xdr:colOff>781050</xdr:colOff>
                     <xdr:row>2</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1033" r:id="rId5" name="Check Box 9">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>1</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>2</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1034" r:id="rId6" name="Check Box 10">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>2</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1035" r:id="rId7" name="Check Box 11">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1036" r:id="rId8" name="Check Box 12">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1037" r:id="rId9" name="Check Box 13">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1038" r:id="rId10" name="Check Box 14">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1039" r:id="rId11" name="Check Box 15">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId12" name="Check Box 68">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId13" name="Check Box 69">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId14" name="Check Box 70">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId15" name="Check Box 71">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId16" name="Check Box 72">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId17" name="Check Box 73">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId18" name="Check Box 74">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId19" name="Check Box 75">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId20" name="Check Box 76">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>17</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId21" name="Check Box 77">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>17</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId22" name="Check Box 78">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId23" name="Check Box 79">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId24" name="Check Box 80">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId25" name="Check Box 81">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId26" name="Check Box 82">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId27" name="Check Box 83">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId28" name="Check Box 84">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId29" name="Check Box 85">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId30" name="Check Box 86">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId31" name="Check Box 87">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId32" name="Check Box 88">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId33" name="Check Box 89">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId34" name="Check Box 90">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>31</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId35" name="Check Box 91">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>32</xdr:row>
-                    <xdr:rowOff>171450</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>33</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId36" name="Check Box 92">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>34</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>35</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId37" name="Check Box 93">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
-                    <xdr:row>32</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>1</xdr:col>
-                    <xdr:colOff>752475</xdr:colOff>
-                    <xdr:row>33</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -8879,92 +5102,89 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
         <v>116</v>
-      </c>
-      <c r="E2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6">
-        <v>2009</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>2009</v>
@@ -8972,47 +5192,44 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7">
-        <v>2019</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="E7">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
@@ -9020,16 +5237,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -9037,16 +5254,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -9054,16 +5271,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -9071,16 +5288,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -9088,16 +5305,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -9105,16 +5322,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -9122,16 +5339,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -9140,7 +5357,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{CAA19930-77F1-4227-B636-30E57F3F0A2A}">
-      <formula1>"Linear time trend, Linear GDP function, Quadratic GDP function, Exponential"</formula1>
+      <formula1>"Linear time trend, Linear GDP function, Ln GDP function, Quadratic GDP function, Exponential"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{54E12EE0-E020-41B3-A703-D02829F27DF0}">
       <formula1>"exp, lin"</formula1>
@@ -9227,7 +5444,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E5C615-F815-41AB-BEEF-C7C927BFC703}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -9244,39 +5461,39 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="4" t="b">
@@ -9289,13 +5506,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -9306,11 +5523,11 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -9323,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -9337,10 +5554,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C4" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -9349,13 +5566,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -9366,10 +5583,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -9381,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="H5" s="4">
         <v>100</v>
@@ -9395,7 +5612,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="b">
         <v>1</v>
@@ -9407,16 +5624,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -9424,7 +5641,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="b">
         <v>1</v>
@@ -9436,16 +5653,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -9453,7 +5670,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="b">
         <v>1</v>
@@ -9464,17 +5681,14 @@
       <c r="E8" s="4">
         <v>0</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>115</v>
+      <c r="F8" s="9">
+        <v>70</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -9482,7 +5696,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="b">
         <v>1</v>
@@ -9493,17 +5707,15 @@
       <c r="E9" s="4">
         <v>0</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>115</v>
+      <c r="F9" s="9">
+        <f>100-F8</f>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="J9" s="4">
         <v>0</v>
@@ -9511,10 +5723,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -9523,13 +5735,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -9540,10 +5752,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -9555,7 +5767,7 @@
         <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="H11" s="4">
         <v>100</v>
@@ -9569,10 +5781,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -9584,7 +5796,7 @@
         <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="H12" s="4">
         <v>100</v>
@@ -9598,10 +5810,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -9613,7 +5825,7 @@
         <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="H13" s="4">
         <v>100</v>
@@ -9627,10 +5839,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -9642,7 +5854,7 @@
         <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="H14" s="4">
         <v>100</v>
@@ -9656,7 +5868,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C15" s="4" t="b">
         <v>1</v>
@@ -9671,13 +5883,13 @@
         <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="H15" s="4">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="4">
         <v>0</v>
@@ -9685,30 +5897,28 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D16">
-        <f>D11</f>
         <v>0</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
       </c>
-      <c r="F16" s="9">
-        <f>100-F11</f>
-        <v>0</v>
+      <c r="F16">
+        <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="H16" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J16" s="4">
         <v>0</v>
@@ -9716,24 +5926,23 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C17" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <f t="shared" ref="D17:D20" si="0">D12</f>
         <v>0</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" ref="F17:F20" si="1">100-F12</f>
+        <f>100-F11</f>
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H17" s="4">
         <v>0</v>
@@ -9747,24 +5956,23 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C18" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="1"/>
+        <f>100-F12</f>
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H18" s="4">
         <v>0</v>
@@ -9778,24 +5986,23 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C19" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="1"/>
+        <f>100-F13</f>
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H19" s="4">
         <v>0</v>
@@ -9809,24 +6016,23 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="1"/>
+        <f>100-F14</f>
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H20" s="4">
         <v>0</v>
@@ -9840,7 +6046,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="C21" s="4" t="b">
         <v>1</v>
@@ -9851,17 +6057,18 @@
       <c r="E21" s="4">
         <v>0</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>41</v>
+      <c r="F21" s="9">
+        <f>100-F15</f>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>41</v>
+        <v>91</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J21" s="4">
         <v>0</v>
@@ -9869,28 +6076,30 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C22" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D22">
+        <f t="shared" ref="D22" si="0">D16</f>
         <v>0</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>41</v>
+      <c r="F22" s="9">
+        <f t="shared" ref="F22" si="1">100-F16</f>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>115</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>41</v>
+        <v>91</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J22" s="4">
         <v>0</v>
@@ -9898,66 +6107,124 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="H23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
         <v>0.33</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="6">
+      <c r="F25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6">
         <v>0.7</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E26" s="8">
         <v>0.7</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I24" s="6">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8">
+      <c r="F26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="6">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="F16:F20" name="Linked values"/>
+    <protectedRange sqref="F17:F22" name="Linked values"/>
   </protectedRanges>
   <dataValidations count="5">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activate subsectors" prompt="Activate calculation and forecast of industrial subsectors._x000a_Unspecified subsector is automaticaly activated." sqref="B1" xr:uid="{949AC99B-8518-4C69-BDE9-CBF83CDC4BE9}"/>
@@ -10201,14 +6468,14 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>161925</xdr:rowOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10223,13 +6490,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>19</xdr:row>
+                    <xdr:row>21</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>21</xdr:row>
+                    <xdr:row>23</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10245,13 +6512,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>20</xdr:row>
+                    <xdr:row>22</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>22</xdr:row>
+                    <xdr:row>24</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10267,13 +6534,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>22</xdr:row>
+                    <xdr:row>24</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>23</xdr:row>
+                    <xdr:row>25</xdr:row>
                     <xdr:rowOff>47625</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10311,13 +6578,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>14</xdr:row>
+                    <xdr:row>15</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>16</xdr:row>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10333,13 +6600,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>17</xdr:row>
+                    <xdr:row>18</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>19</xdr:row>
+                    <xdr:row>20</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10355,13 +6622,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>18</xdr:row>
+                    <xdr:row>20</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>20</xdr:row>
+                    <xdr:row>22</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10377,13 +6644,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>16</xdr:row>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>18</xdr:row>
+                    <xdr:row>19</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10399,13 +6666,13 @@
                   <from>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>19050</xdr:colOff>
-                    <xdr:row>15</xdr:row>
+                    <xdr:row>16</xdr:row>
                     <xdr:rowOff>161925</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
                     <xdr:colOff>742950</xdr:colOff>
-                    <xdr:row>17</xdr:row>
+                    <xdr:row>18</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </to>
                 </anchor>
@@ -10451,6 +6718,72 @@
                     <xdr:colOff>742950</xdr:colOff>
                     <xdr:row>4</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="11307" r:id="rId26" name="Check Box 43">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>161925</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>733425</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="11308" r:id="rId27" name="Check Box 44">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>171450</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="11309" r:id="rId28" name="Check Box 45">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>1</xdr:col>
+                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -10474,27 +6807,27 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>0.45</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="D2">
         <v>0.45</v>
@@ -10502,13 +6835,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>0.83115000000000006</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="D3">
         <v>0.83115000000000006</v>
@@ -10516,55 +6849,55 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="B7" s="12">
         <v>0</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="D7" s="12">
         <v>0</v>
@@ -10572,13 +6905,13 @@
     </row>
     <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10586,13 +6919,13 @@
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -10621,98 +6954,98 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>2018</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="E6">
         <v>2018</v>
@@ -10775,69 +7108,69 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>2019</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>2019</v>
@@ -10845,16 +7178,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>0.5</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="E6">
         <v>0.5</v>
@@ -10862,16 +7195,16 @@
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
@@ -10879,16 +7212,16 @@
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E8">
         <v>0</v>

--- a/input/Set_and_Control_Parameters.xlsx
+++ b/input/Set_and_Control_Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo_Projects\endemo-ENS\endemo_IND_world_branch\endemo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D5FFDC-7AD7-4001-B453-C55B6F0DFA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB2B050-531E-41AB-881C-47446772453C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="1020" windowWidth="20175" windowHeight="13230" tabRatio="730" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33600" yWindow="1440" windowWidth="20175" windowHeight="13230" tabRatio="730" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralSettings" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="133">
   <si>
     <t>Country</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>Last considered year</t>
+  </si>
+  <si>
+    <t>Production quantity upper limit (unit description)</t>
   </si>
 </sst>
 </file>
@@ -569,7 +572,7 @@
       <alignment horizontal="right"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -595,6 +598,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -764,11 +770,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$8" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$8" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$9" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$9" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1919,15 +1925,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>9525</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>352425</xdr:rowOff>
+          <xdr:rowOff>561975</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>742950</xdr:colOff>
+          <xdr:colOff>733425</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
+          <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4735,7 +4741,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -4749,7 +4755,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -5451,7 +5457,7 @@
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="56.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -5459,7 +5465,7 @@
     <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -5472,8 +5478,8 @@
       <c r="D1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>49</v>
+      <c r="E1" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>77</v>
@@ -5502,9 +5508,7 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="9" t="s">
         <v>7</v>
       </c>
@@ -5532,9 +5536,7 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="9">
         <f>100-F5</f>
         <v>0</v>
@@ -5562,9 +5564,7 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5591,9 +5591,7 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
+      <c r="E5" s="4"/>
       <c r="F5">
         <v>100</v>
       </c>
@@ -5620,9 +5618,7 @@
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="9" t="s">
         <v>7</v>
       </c>
@@ -5649,9 +5645,7 @@
       <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="9" t="s">
         <v>7</v>
       </c>
@@ -5678,9 +5672,7 @@
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="9">
         <v>70</v>
       </c>
@@ -5704,9 +5696,7 @@
       <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="9">
         <f>100-F8</f>
         <v>30</v>
@@ -5731,9 +5721,7 @@
       <c r="D10">
         <v>0</v>
       </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="9" t="s">
         <v>7</v>
       </c>
@@ -5760,9 +5748,7 @@
       <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
+      <c r="E11" s="4"/>
       <c r="F11">
         <v>100</v>
       </c>
@@ -5789,9 +5775,7 @@
       <c r="D12">
         <v>0</v>
       </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
+      <c r="E12" s="4"/>
       <c r="F12">
         <v>100</v>
       </c>
@@ -5818,9 +5802,7 @@
       <c r="D13">
         <v>0</v>
       </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
+      <c r="E13" s="4"/>
       <c r="F13">
         <v>100</v>
       </c>
@@ -5847,9 +5829,7 @@
       <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
+      <c r="E14" s="4"/>
       <c r="F14">
         <v>100</v>
       </c>
@@ -5877,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>6.4399999999999999E-2</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -5906,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -5934,9 +5914,7 @@
       <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="9">
         <f>100-F11</f>
         <v>0</v>
@@ -5964,9 +5942,7 @@
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="9">
         <f>100-F12</f>
         <v>0</v>
@@ -5994,9 +5970,7 @@
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
+      <c r="E19" s="4"/>
       <c r="F19" s="9">
         <f>100-F13</f>
         <v>0</v>
@@ -6024,9 +5998,7 @@
       <c r="D20">
         <v>0</v>
       </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
+      <c r="E20" s="4"/>
       <c r="F20" s="9">
         <f>100-F14</f>
         <v>0</v>
@@ -6055,7 +6027,8 @@
         <v>0</v>
       </c>
       <c r="E21" s="4">
-        <v>0</v>
+        <f>E15</f>
+        <v>6.4399999999999999E-2</v>
       </c>
       <c r="F21" s="9">
         <f>100-F15</f>
@@ -6086,7 +6059,8 @@
         <v>0</v>
       </c>
       <c r="E22" s="4">
-        <v>0</v>
+        <f>E16</f>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F22" s="9">
         <f t="shared" ref="F22" si="1">100-F16</f>
@@ -6115,9 +6089,7 @@
       <c r="D23">
         <v>0</v>
       </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="9" t="s">
         <v>7</v>
       </c>
@@ -6144,9 +6116,7 @@
       <c r="D24">
         <v>0</v>
       </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
+      <c r="E24" s="4"/>
       <c r="F24" s="9" t="s">
         <v>7</v>
       </c>
@@ -6173,9 +6143,7 @@
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="4">
-        <v>0.33</v>
-      </c>
+      <c r="E25" s="4"/>
       <c r="F25" s="9" t="s">
         <v>7</v>
       </c>
@@ -6203,9 +6171,7 @@
       <c r="D26" s="6">
         <v>0.7</v>
       </c>
-      <c r="E26" s="8">
-        <v>0.7</v>
-      </c>
+      <c r="E26" s="8"/>
       <c r="F26" s="10" t="s">
         <v>7</v>
       </c>
@@ -6226,12 +6192,13 @@
   <protectedRanges>
     <protectedRange sqref="F17:F22" name="Linked values"/>
   </protectedRanges>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Activate subsectors" prompt="Activate calculation and forecast of industrial subsectors._x000a_Unspecified subsector is automaticaly activated." sqref="B1" xr:uid="{949AC99B-8518-4C69-BDE9-CBF83CDC4BE9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Show status" prompt="Shows status of industrial subsector activation" sqref="C1" xr:uid="{D39270FC-1E17-4BF1-A784-B322B986174F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Production quantity development" prompt="User defined expectation for the yearly development from last available historical year or pregiven value till the forecasted year._x000a_To be applied with exponential function of production quantity extrapolation or if not enough data are available." sqref="D1" xr:uid="{B759DEDC-FFC7-4AED-960F-A7EC37EB9FCC}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Technology substitution" prompt="User defined expectation for the forecasted year" sqref="F1" xr:uid="{5BCC82F2-3048-4B59-9F52-5232CB2E59D7}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Prod. efficiency development" prompt="User defined expectation for the yearly change of the efficiency (applied on the pregiven value)_x000a_Applies only if the Trend calculation for specific energy requirements is disactivated." sqref="I1" xr:uid="{EA236F94-8106-431A-8B80-F2F9E2C16CB9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Unit:" prompt="If calculation of the production quantity per capita is selected (see IND_general), then the unit is ton per capita._x000a_Otherwise, the unit is ton." sqref="E1" xr:uid="{C2BCDC4E-2C12-4FC3-BF03-7951C5B34506}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6247,15 +6214,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>9525</xdr:colOff>
                     <xdr:row>0</xdr:row>
-                    <xdr:rowOff>352425</xdr:rowOff>
+                    <xdr:rowOff>561975</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>742950</xdr:colOff>
+                    <xdr:colOff>733425</xdr:colOff>
                     <xdr:row>2</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
+                    <xdr:rowOff>38100</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
